--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484865_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484865_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7185</v>
+        <v>5.285</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1697</v>
+        <v>6.6569</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.4512</v>
+        <v>-1.3719</v>
       </c>
       <c r="G2" t="n">
         <v>5.2651</v>
@@ -610,13 +610,13 @@
         <v>0.9435</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.5648</v>
+        <v>-0.9983</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.117</v>
+        <v>-0.6298</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4479</v>
+        <v>-0.3685</v>
       </c>
       <c r="V2" t="n">
         <v>4.0374</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. BLEDA MIRANDA</t>
+          <t>J. MUNOZ PALENCIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6635</v>
+        <v>3.155</v>
       </c>
       <c r="E3" t="n">
-        <v>4.446</v>
+        <v>5.8943</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.7825</v>
+        <v>-2.7393</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1983</v>
+        <v>6.4057</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6395</v>
+        <v>-0.45</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5588</v>
+        <v>6.8557</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2612</v>
+        <v>7.7359</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3564</v>
+        <v>1.1622</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9049</v>
+        <v>6.5738</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0629</v>
+        <v>-1.3302</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7168</v>
+        <v>-1.6121</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3461</v>
+        <v>0.2819</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.5096</v>
+        <v>-1.6983</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0757</v>
+        <v>-3.0192</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5661</v>
+        <v>1.3209</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7295</v>
+        <v>-0.9488</v>
       </c>
       <c r="T3" t="n">
-        <v>0.77</v>
+        <v>-0.6902</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0405</v>
+        <v>-0.2585</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2452</v>
+        <v>-0.6036</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4904</v>
+        <v>1.8678</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2452</v>
+        <v>-2.4714</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MUNOZ PALENCIA</t>
+          <t>C. BLEDA MIRANDA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5608</v>
+        <v>1.9201</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1148</v>
+        <v>3.8614</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.5541</v>
+        <v>-1.9412</v>
       </c>
       <c r="G4" t="n">
-        <v>6.4057</v>
+        <v>2.1983</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.45</v>
+        <v>1.6395</v>
       </c>
       <c r="I4" t="n">
-        <v>6.8557</v>
+        <v>0.5588</v>
       </c>
       <c r="J4" t="n">
-        <v>7.7359</v>
+        <v>3.2612</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1622</v>
+        <v>2.3564</v>
       </c>
       <c r="L4" t="n">
-        <v>6.5738</v>
+        <v>0.9049</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3302</v>
+        <v>-1.0629</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.6121</v>
+        <v>-0.7168</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2819</v>
+        <v>-0.3461</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.6983</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.0192</v>
+        <v>-2.0757</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3209</v>
+        <v>0.5661</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.543</v>
+        <v>-0.0138</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.4697</v>
+        <v>0.1854</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.07340000000000001</v>
+        <v>-0.1992</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6036</v>
+        <v>1.2452</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8678</v>
+        <v>2.4904</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.4714</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="5">
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. FEDOROV</t>
+          <t>I. DE ANDREA LUNA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-1.2189</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0036</v>
+        <v>-0.4809</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.858</v>
+        <v>-0.738</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6597</v>
+        <v>-1.3417</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.5105</v>
+        <v>-0.6425</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8509</v>
+        <v>-0.6992</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3557</v>
+        <v>-0.4205</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6073</v>
+        <v>0.1057</v>
       </c>
       <c r="L6" t="n">
-        <v>0.963</v>
+        <v>-0.5262</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0154</v>
+        <v>-0.9212</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.9032</v>
+        <v>-0.7482</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8878</v>
+        <v>-0.173</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3774</v>
+        <v>0.3774</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1322</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7548</v>
+        <v>0.3774</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4656</v>
+        <v>0.0472</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5349</v>
+        <v>-0.0604</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0693</v>
+        <v>0.1076</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2828</v>
+        <v>-0.3018</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.528</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. DE ANDREA LUNA</t>
+          <t>K. FEDOROV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6964</v>
+        <v>-1.5712</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7732</v>
+        <v>0.419</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9232</v>
+        <v>-1.9902</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3417</v>
+        <v>-0.6597</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6425</v>
+        <v>-2.5105</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6992</v>
+        <v>1.8509</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4205</v>
+        <v>0.3557</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1057</v>
+        <v>-0.6073</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5262</v>
+        <v>0.963</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9212</v>
+        <v>-1.0154</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7482</v>
+        <v>-1.9032</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.173</v>
+        <v>0.8878</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3774</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1322</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3774</v>
+        <v>0.7548</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4303</v>
+        <v>-0.2513</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3527</v>
+        <v>-0.0497</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0776</v>
+        <v>-0.2016</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3018</v>
+        <v>-0.2828</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3018</v>
+        <v>-1.528</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.3295</v>
+        <v>-2.8612</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8896</v>
+        <v>1.305</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.2191</v>
+        <v>-4.1662</v>
       </c>
       <c r="G8" t="n">
         <v>1.895</v>
@@ -1078,13 +1078,13 @@
         <v>0.9435</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.602</v>
+        <v>-1.1336</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1234</v>
+        <v>-0.4612</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7252999999999999</v>
+        <v>-0.6724</v>
       </c>
       <c r="V8" t="n">
         <v>-3.4338</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.8983</v>
+        <v>-4.9693</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.1239</v>
+        <v>-4.2213</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7745</v>
+        <v>-0.748</v>
       </c>
       <c r="G9" t="n">
         <v>-1.6616</v>
@@ -1156,13 +1156,13 @@
         <v>0.3774</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1599</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1793</v>
+        <v>0.0818</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0194</v>
+        <v>0.0071</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.9957</v>
+        <v>-7.5711</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.8192</v>
+        <v>-5.5269</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1765</v>
+        <v>-2.0442</v>
       </c>
       <c r="G10" t="n">
         <v>-5.9349</v>
@@ -1234,13 +1234,13 @@
         <v>1.3209</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1739</v>
+        <v>-0.7494</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.5278</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3538</v>
+        <v>-0.2215</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3208</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.897500000000002</v>
+        <v>-6.897699999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>8.8413</v>
+        <v>8.8414</v>
       </c>
       <c r="F11" t="n">
-        <v>-15.7391</v>
+        <v>-15.739</v>
       </c>
       <c r="G11" t="n">
         <v>7.1001</v>
@@ -1288,7 +1288,7 @@
         <v>15.864</v>
       </c>
       <c r="K11" t="n">
-        <v>2.120899999999999</v>
+        <v>2.1209</v>
       </c>
       <c r="L11" t="n">
         <v>13.7434</v>
@@ -1312,13 +1312,13 @@
         <v>6.6045</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.959</v>
+        <v>-3.9591</v>
       </c>
       <c r="T11" t="n">
         <v>-2.1519</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.8072</v>
+        <v>-1.807</v>
       </c>
       <c r="V11" t="n">
         <v>0.3398000000000005</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.3024</v>
+        <v>8.878299999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>10.1599</v>
+        <v>9.185600000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1425</v>
+        <v>-0.3073</v>
       </c>
       <c r="G12" t="n">
         <v>-0.09180000000000001</v>
@@ -1390,13 +1390,13 @@
         <v>3.3966</v>
       </c>
       <c r="S12" t="n">
-        <v>2.9792</v>
+        <v>1.5551</v>
       </c>
       <c r="T12" t="n">
-        <v>1.8369</v>
+        <v>0.8626</v>
       </c>
       <c r="U12" t="n">
-        <v>1.1423</v>
+        <v>0.6926</v>
       </c>
       <c r="V12" t="n">
         <v>4.9618</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. LOPEZ-VALVERDE CARRASCO</t>
+          <t>C. SEVERA LENCINA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.9943</v>
+        <v>2.3521</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2476</v>
+        <v>3.9489</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2534</v>
+        <v>-1.5968</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.8562</v>
+        <v>0.5656</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1746</v>
+        <v>0.6824</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6816</v>
+        <v>-0.1169</v>
       </c>
       <c r="J13" t="n">
-        <v>1.4126</v>
+        <v>2.5853</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0383</v>
+        <v>1.2521</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3743</v>
+        <v>1.3332</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.2688</v>
+        <v>-2.0198</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2128</v>
+        <v>-0.5697</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.056</v>
+        <v>-1.4501</v>
       </c>
       <c r="P13" t="n">
-        <v>2.0757</v>
+        <v>2.6418</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1322</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.2079</v>
+        <v>2.6418</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7748</v>
+        <v>0.409</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4202</v>
+        <v>0.1373</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3545</v>
+        <v>0.2716</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-1.2642</v>
       </c>
       <c r="W13" t="n">
-        <v>1.547</v>
+        <v>1.2262</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.547</v>
+        <v>-2.4904</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. SERNEGUET GARVI</t>
+          <t>P. LOPEZ-VALVERDE CARRASCO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8459</v>
+        <v>2.1265</v>
       </c>
       <c r="E14" t="n">
-        <v>4.863</v>
+        <v>2.2476</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.0171</v>
+        <v>-0.1211</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2124</v>
+        <v>-0.8562</v>
       </c>
       <c r="H14" t="n">
-        <v>2.7664</v>
+        <v>-0.1746</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.5541</v>
+        <v>-0.6816</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4278</v>
+        <v>1.4126</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2548</v>
+        <v>0.0383</v>
       </c>
       <c r="L14" t="n">
-        <v>0.173</v>
+        <v>1.3743</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.2154</v>
+        <v>-2.2688</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4883</v>
+        <v>-0.2128</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.7271</v>
+        <v>-2.056</v>
       </c>
       <c r="P14" t="n">
         <v>2.0757</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9435</v>
+        <v>-1.1322</v>
       </c>
       <c r="R14" t="n">
-        <v>3.0192</v>
+        <v>3.2079</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3691</v>
+        <v>0.907</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8317</v>
+        <v>0.4202</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5373</v>
+        <v>0.4868</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.8112</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>1.547</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.3582</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. SEVERA LENCINA</t>
+          <t>A. SERNEGUET GARVI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4682</v>
+        <v>1.1581</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4617</v>
+        <v>4.863</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.9936</v>
+        <v>-3.7049</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5656</v>
+        <v>0.2124</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6824</v>
+        <v>2.7664</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1169</v>
+        <v>-2.5541</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5853</v>
+        <v>3.4278</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2521</v>
+        <v>3.2548</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3332</v>
+        <v>0.173</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0198</v>
+        <v>-3.2154</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5697</v>
+        <v>-0.4883</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.4501</v>
+        <v>-2.7271</v>
       </c>
       <c r="P15" t="n">
-        <v>2.6418</v>
+        <v>2.0757</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R15" t="n">
-        <v>2.6418</v>
+        <v>3.0192</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.475</v>
+        <v>1.6812</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3498</v>
+        <v>0.8317</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1252</v>
+        <v>0.8495</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2642</v>
+        <v>-2.8112</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2262</v>
+        <v>1.547</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.4904</v>
+        <v>-4.3582</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7241</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2227</v>
+        <v>0.4175</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9467</v>
+        <v>-0.3383</v>
       </c>
       <c r="G16" t="n">
         <v>0.0024</v>
@@ -1702,13 +1702,13 @@
         <v>2.8305</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5567</v>
+        <v>0.2466</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.053</v>
+        <v>0.1419</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5038</v>
+        <v>0.1047</v>
       </c>
       <c r="V16" t="n">
         <v>0.019</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1883</v>
+        <v>-1.0115</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6931</v>
+        <v>-0.5956</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4952</v>
+        <v>-0.4159</v>
       </c>
       <c r="G17" t="n">
         <v>-0.9349</v>
@@ -1780,13 +1780,13 @@
         <v>0.3774</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4421</v>
+        <v>-0.2653</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2352</v>
+        <v>-0.1377</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2069</v>
+        <v>-0.1276</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6901</v>
+        <v>-1.7875</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3115</v>
+        <v>-1.409</v>
       </c>
       <c r="F18" t="n">
         <v>-0.3785</v>
@@ -1858,10 +1858,10 @@
         <v>0.5661</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0711</v>
+        <v>-0.0263</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0029</v>
+        <v>-0.0945</v>
       </c>
       <c r="U18" t="n">
         <v>0.0682</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.1106</v>
+        <v>-4.8977</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.2114</v>
+        <v>-2.9191</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8992</v>
+        <v>-1.9786</v>
       </c>
       <c r="G19" t="n">
         <v>-3.8589</v>
@@ -1936,13 +1936,13 @@
         <v>0.9435</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7613</v>
+        <v>-0.5483</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.3544</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1146</v>
+        <v>-0.194</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2452</v>
@@ -1969,19 +1969,19 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>6.8977</v>
+        <v>6.897500000000001</v>
       </c>
       <c r="E20" t="n">
         <v>15.7389</v>
       </c>
       <c r="F20" t="n">
-        <v>-8.841200000000001</v>
+        <v>-8.8414</v>
       </c>
       <c r="G20" t="n">
         <v>-7.100000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>8.0526</v>
+        <v>8.052600000000002</v>
       </c>
       <c r="I20" t="n">
         <v>-15.1529</v>
@@ -2014,16 +2014,16 @@
         <v>16.983</v>
       </c>
       <c r="S20" t="n">
-        <v>3.959099999999999</v>
+        <v>3.959</v>
       </c>
       <c r="T20" t="n">
-        <v>1.807</v>
+        <v>1.8071</v>
       </c>
       <c r="U20" t="n">
         <v>2.1518</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3398000000000001</v>
+        <v>-0.3397999999999997</v>
       </c>
       <c r="W20" t="n">
         <v>11.7724</v>
